--- a/jogos_2024-12-31.xlsx
+++ b/jogos_2024-12-31.xlsx
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,19 +1159,19 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Enyimba</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Bendel Insurance</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -1185,83 +1185,83 @@
         </is>
       </c>
       <c r="L6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N6" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>11</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC6" t="n">
         <v>3.2</v>
       </c>
-      <c r="M6" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="N6" t="n">
-        <v>2</v>
-      </c>
-      <c r="O6" t="n">
-        <v>4</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T6" t="n">
-        <v>3</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X6" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AD6" t="n">
-        <v>1.83</v>
+        <v>1.3</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>['54', '90+1']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>['61']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.65</v>
+        <v>1.07</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.35</v>
+        <v>2.32</v>
       </c>
       <c r="AI6" t="n">
-        <v>2.4</v>
+        <v>1.22</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.67</v>
+        <v>7</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45657.5</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,19 +1288,19 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Enyimba</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bendel Insurance</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -1314,83 +1314,83 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.3</v>
+        <v>3.2</v>
       </c>
       <c r="M7" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="N7" t="n">
-        <v>8.5</v>
+        <v>2</v>
       </c>
       <c r="O7" t="n">
-        <v>1.91</v>
+        <v>4</v>
       </c>
       <c r="P7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y7" t="n">
         <v>2</v>
       </c>
-      <c r="Q7" t="n">
-        <v>11</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S7" t="n">
+      <c r="Z7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>['54', '90+1']</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>['61']</t>
+        </is>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AI7" t="n">
         <v>2.4</v>
       </c>
-      <c r="T7" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="X7" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AJ7" t="n">
-        <v>7</v>
+        <v>1.67</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45657.5</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,22 +1546,22 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1572,83 +1572,83 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="M9" t="n">
-        <v>3.2</v>
+        <v>4.56</v>
       </c>
       <c r="N9" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S9" t="n">
         <v>3</v>
       </c>
-      <c r="O9" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P9" t="n">
+      <c r="T9" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X9" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AC9" t="n">
         <v>2</v>
       </c>
-      <c r="Q9" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="X9" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AD9" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['15', '47']</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['63', '70']</t>
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.62</v>
+        <v>2.16</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.8</v>
+        <v>1.36</v>
       </c>
       <c r="AJ9" t="n">
-        <v>2.3</v>
+        <v>3.25</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45657.61458333334</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,22 +1675,22 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1701,83 +1701,83 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="M10" t="n">
-        <v>4.56</v>
+        <v>3.2</v>
       </c>
       <c r="N10" t="n">
-        <v>5.73</v>
+        <v>3</v>
       </c>
       <c r="O10" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="P10" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.5</v>
+        <v>3.75</v>
       </c>
       <c r="R10" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="T10" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="U10" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="V10" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="W10" t="n">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="X10" t="n">
-        <v>3.55</v>
+        <v>2.95</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.82</v>
+        <v>2.25</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.94</v>
+        <v>1.62</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.05</v>
+        <v>3.8</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="AC10" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>['15', '47']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>['63', '70']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.16</v>
+        <v>1.62</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.36</v>
+        <v>1.8</v>
       </c>
       <c r="AJ10" t="n">
-        <v>3.25</v>
+        <v>2.3</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45657.61458333334</v>
